--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,469 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121592214</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>594780</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7185577</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121592217</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594818</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7185589</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121592218</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>594796</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7185552</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121592215</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594817</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7185591</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592214</v>
+        <v>121592217</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594780</v>
+        <v>594818</v>
       </c>
       <c r="R3" t="n">
-        <v>7185577</v>
+        <v>7185589</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592217</v>
+        <v>121592218</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +929,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594818</v>
+        <v>594796</v>
       </c>
       <c r="R4" t="n">
-        <v>7185589</v>
+        <v>7185552</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592218</v>
+        <v>121592215</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1066,7 +1066,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594796</v>
+        <v>594817</v>
       </c>
       <c r="R5" t="n">
-        <v>7185552</v>
+        <v>7185591</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592215</v>
+        <v>121592214</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594817</v>
+        <v>594780</v>
       </c>
       <c r="R6" t="n">
-        <v>7185591</v>
+        <v>7185577</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592217</v>
+        <v>121592215</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594818</v>
+        <v>594817</v>
       </c>
       <c r="R3" t="n">
-        <v>7185589</v>
+        <v>7185591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -913,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592218</v>
+        <v>121592214</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -949,7 +954,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R4" t="n">
-        <v>7185552</v>
+        <v>7185577</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592215</v>
+        <v>121592218</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1066,7 +1071,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594817</v>
+        <v>594796</v>
       </c>
       <c r="R5" t="n">
-        <v>7185591</v>
+        <v>7185552</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592214</v>
+        <v>121592217</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594780</v>
+        <v>594818</v>
       </c>
       <c r="R6" t="n">
-        <v>7185577</v>
+        <v>7185589</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592215</v>
+        <v>121592214</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594817</v>
+        <v>594780</v>
       </c>
       <c r="R3" t="n">
-        <v>7185591</v>
+        <v>7185577</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592214</v>
+        <v>121592215</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594780</v>
+        <v>594817</v>
       </c>
       <c r="R4" t="n">
-        <v>7185577</v>
+        <v>7185591</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592218</v>
+        <v>121592217</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,39 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594796</v>
+        <v>594818</v>
       </c>
       <c r="R5" t="n">
-        <v>7185552</v>
+        <v>7185589</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592217</v>
+        <v>121592218</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594818</v>
+        <v>594796</v>
       </c>
       <c r="R6" t="n">
-        <v>7185589</v>
+        <v>7185552</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592214</v>
+        <v>121592217</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594780</v>
+        <v>594818</v>
       </c>
       <c r="R3" t="n">
-        <v>7185577</v>
+        <v>7185589</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592215</v>
+        <v>121592218</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -954,7 +949,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594817</v>
+        <v>594796</v>
       </c>
       <c r="R4" t="n">
-        <v>7185591</v>
+        <v>7185552</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592217</v>
+        <v>121592215</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,34 +1046,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594818</v>
+        <v>594817</v>
       </c>
       <c r="R5" t="n">
-        <v>7185589</v>
+        <v>7185591</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592218</v>
+        <v>121592214</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1183,7 +1183,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R6" t="n">
-        <v>7185552</v>
+        <v>7185577</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592214</v>
+        <v>121592217</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594780</v>
+        <v>594818</v>
       </c>
       <c r="R3" t="n">
-        <v>7185577</v>
+        <v>7185589</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1152,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592217</v>
+        <v>121592214</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594818</v>
+        <v>594780</v>
       </c>
       <c r="R6" t="n">
-        <v>7185589</v>
+        <v>7185577</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592217</v>
+        <v>121592215</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594818</v>
+        <v>594817</v>
       </c>
       <c r="R3" t="n">
-        <v>7185589</v>
+        <v>7185591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1030,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592215</v>
+        <v>121592214</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1075,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594817</v>
+        <v>594780</v>
       </c>
       <c r="R5" t="n">
-        <v>7185591</v>
+        <v>7185577</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592214</v>
+        <v>121592217</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594780</v>
+        <v>594818</v>
       </c>
       <c r="R6" t="n">
-        <v>7185577</v>
+        <v>7185589</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592215</v>
+        <v>121592214</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594817</v>
+        <v>594780</v>
       </c>
       <c r="R3" t="n">
-        <v>7185591</v>
+        <v>7185577</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592218</v>
+        <v>121592217</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,39 +934,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594796</v>
+        <v>594818</v>
       </c>
       <c r="R4" t="n">
-        <v>7185552</v>
+        <v>7185589</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592214</v>
+        <v>121592215</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1080,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594780</v>
+        <v>594817</v>
       </c>
       <c r="R5" t="n">
-        <v>7185577</v>
+        <v>7185591</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592217</v>
+        <v>121592218</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594818</v>
+        <v>594796</v>
       </c>
       <c r="R6" t="n">
-        <v>7185589</v>
+        <v>7185552</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592214</v>
+        <v>121592217</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594780</v>
+        <v>594818</v>
       </c>
       <c r="R3" t="n">
-        <v>7185577</v>
+        <v>7185589</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592217</v>
+        <v>121592214</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +929,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594818</v>
+        <v>594780</v>
       </c>
       <c r="R4" t="n">
-        <v>7185589</v>
+        <v>7185577</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592215</v>
+        <v>121592218</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1066,7 +1066,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594817</v>
+        <v>594796</v>
       </c>
       <c r="R5" t="n">
-        <v>7185591</v>
+        <v>7185552</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592218</v>
+        <v>121592215</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1183,7 +1183,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594796</v>
+        <v>594817</v>
       </c>
       <c r="R6" t="n">
-        <v>7185552</v>
+        <v>7185591</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592217</v>
+        <v>121592214</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594818</v>
+        <v>594780</v>
       </c>
       <c r="R3" t="n">
-        <v>7185589</v>
+        <v>7185577</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592214</v>
+        <v>121592217</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +934,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594780</v>
+        <v>594818</v>
       </c>
       <c r="R4" t="n">
-        <v>7185577</v>
+        <v>7185589</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592214</v>
+        <v>121592218</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -837,7 +837,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594780</v>
+        <v>594796</v>
       </c>
       <c r="R3" t="n">
-        <v>7185577</v>
+        <v>7185552</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592217</v>
+        <v>121592215</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +934,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594818</v>
+        <v>594817</v>
       </c>
       <c r="R4" t="n">
-        <v>7185589</v>
+        <v>7185591</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1030,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592218</v>
+        <v>121592214</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1066,7 +1071,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594796</v>
+        <v>594780</v>
       </c>
       <c r="R5" t="n">
-        <v>7185552</v>
+        <v>7185577</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592215</v>
+        <v>121592217</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594817</v>
+        <v>594818</v>
       </c>
       <c r="R6" t="n">
-        <v>7185591</v>
+        <v>7185589</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592214</v>
+        <v>121592217</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,39 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594780</v>
+        <v>594818</v>
       </c>
       <c r="R5" t="n">
-        <v>7185577</v>
+        <v>7185589</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592217</v>
+        <v>121592214</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594818</v>
+        <v>594780</v>
       </c>
       <c r="R6" t="n">
-        <v>7185589</v>
+        <v>7185577</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121592218</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592215</v>
+        <v>121592217</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,39 +934,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594817</v>
+        <v>594818</v>
       </c>
       <c r="R4" t="n">
-        <v>7185591</v>
+        <v>7185589</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1035,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592217</v>
+        <v>121592214</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,34 +1046,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594818</v>
+        <v>594780</v>
       </c>
       <c r="R5" t="n">
-        <v>7185589</v>
+        <v>7185577</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592214</v>
+        <v>121592215</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594780</v>
+        <v>594817</v>
       </c>
       <c r="R6" t="n">
-        <v>7185577</v>
+        <v>7185591</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41646-2024 artfynd.xlsx
+++ b/artfynd/A 41646-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>56145611</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594823.0340648554</v>
+        <v>594823</v>
       </c>
       <c r="R2" t="n">
-        <v>7185526.846394316</v>
+        <v>7185527</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-08-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,55 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592218</v>
+        <v>121592217</v>
       </c>
       <c r="B3" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594796</v>
+        <v>594818</v>
       </c>
       <c r="R3" t="n">
-        <v>7185552</v>
+        <v>7185589</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592217</v>
+        <v>121592214</v>
       </c>
       <c r="B4" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,34 +904,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594818</v>
+        <v>594780</v>
       </c>
       <c r="R4" t="n">
-        <v>7185589</v>
+        <v>7185577</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592214</v>
+        <v>121592215</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594780</v>
+        <v>594817</v>
       </c>
       <c r="R5" t="n">
-        <v>7185577</v>
+        <v>7185591</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,15 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592215</v>
+        <v>121592218</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1148,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594817</v>
+        <v>594796</v>
       </c>
       <c r="R6" t="n">
-        <v>7185591</v>
+        <v>7185552</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
